--- a/gex_pivot_levels_2026-09-11.xlsx
+++ b/gex_pivot_levels_2026-09-11.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$8.77M</t>
+          <t>-$6.74M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$8.85M</t>
+          <t>+$6.81M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -577,12 +577,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$1.67M</t>
+          <t>-$1.31M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$1.85M</t>
+          <t>+$1.45M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$21.92M</t>
+          <t>-$17.54M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$23.81M</t>
+          <t>+$19.05M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$975.69K</t>
+          <t>-$746.11K</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$1.19M</t>
+          <t>+$907.97K</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -663,196 +663,200 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>7524.31</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>-$26.80M</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>+$29.47M</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-$45.40M</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+$49.32M</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>7561.05</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>7550</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>-$18.08M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>+$20.03M</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A7" s="5" t="n">
+        <v>7534.33</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>751</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>-$10.08M</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>+$13.56M</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
+        <v>7561.05</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7550</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>-$15.75M</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>+$17.44M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>7574.4</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>755</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>-$112.05M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+$119.12M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-$171.90M</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+$184.64M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>7576.05</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>7565</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>-$2.92M</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>+$4.20M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-$2.61M</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>+$3.75M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="11">
+      <c r="A11" s="2" t="n">
         <v>7581.05</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>7570</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-$10.77M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$11.90M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>-$9.66M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$10.68M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>7584.42</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>756</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$7.50M</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$11.20M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
@@ -870,12 +874,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>-$7.67M</t>
+          <t>-$7.19M</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>+$16.79M</t>
+          <t>+$15.72M</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -899,12 +903,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-$20.95M</t>
+          <t>-$20.57M</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+$35.22M</t>
+          <t>+$67.82M</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -928,12 +932,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>-$2.36M</t>
+          <t>-$2.27M</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>+$34.76M</t>
+          <t>+$33.40M</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -944,350 +948,490 @@
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
+        <v>7614.47</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>759</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$5.22M</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>+$47.45M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
         <v>7624.49</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>760</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>-$180.38M</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>+$192.97M</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>-$155.05M</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+$248.56M</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>7641.05</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>7630</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$5.36M</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>+$21.05M</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>7644.52</v>
+        <v>7641.05</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>762</v>
+        <v>7630</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>+$3.09M</t>
+          <t>+$5.45M</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>+$29.91M</t>
+          <t>+$21.41M</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
+        <v>7644.52</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>762</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+$16.37M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+$41.09M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
         <v>7646.05</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B19" s="5" t="n">
         <v>7635</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>+$7.86M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$18.20M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>+$8.12M</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>+$18.82M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>7654.54</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>-$81.90M</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>+$127.25M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
+        <v>7654.54</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>763</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>-$42.09M</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>+$106.57M</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
         <v>7661.05</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>7650</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>-$2.95M</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>+$36.05M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>-$3.15M</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>+$38.54M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
+    <row r="22">
+      <c r="A22" s="2" t="n">
         <v>7671.05</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B22" s="2" t="n">
         <v>7660</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>+$9.23M</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>+$16.47M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>+$10.06M</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>+$17.94M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>7674.58</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>+$23.93M</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>+$62.50M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>7674.58</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+$6.02M</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>+$49.95M</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>7686.05</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>7675</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>+$12.19M</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>+$20.68M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
+        <v>7676.05</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>7665</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>+$5.17M</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>+$13.87M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>7686.05</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>7675</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>+$14.22M</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>+$24.13M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>7691.05</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7680</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>+$4.11M</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>+$15.64M</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>7696.05</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>7685</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>+$9.32M</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>+$14.72M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
         <v>7711.05</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>7700</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>+$4.78M</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>+$25.15M</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>+$5.85M</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>+$30.82M</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>7724.67</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B29" s="2" t="n">
         <v>770</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>+$18.54M</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>+$34.95M</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>+$34.85M</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>+$35.65M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G25"/>
+  <autoFilter ref="A1:G29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1299,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1350,72 +1494,68 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
+        <v>28302.46</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>-$8.23M</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>+$8.41M</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>28507.8</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B3" s="5" t="n">
         <v>695</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>-$10.32M</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>+$10.78M</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>-$12.81M</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>+$13.32M</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>28713.13</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>-$26.08M</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>+$30.56M</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>28795.26</v>
+        <v>28631</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -1424,45 +1564,41 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>-$2.61M</t>
+          <t>-$10.83M</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>+$3.48M</t>
+          <t>+$11.52M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>28866.49</v>
+        <v>28713.13</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>28900</v>
+        <v>700</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-$158.32K</t>
+          <t>-$30.25M</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+$172.29K</t>
+          <t>+$37.03M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1478,72 +1614,76 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>28891.49</v>
+        <v>28754.2</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>28925</v>
+        <v>701</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>-$4.61M</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>+$7.71M</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>28866.49</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>28900</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>-$13.10K</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>+$55.01K</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>28906.49</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>28940</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+$10.48K</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-$158.32K</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+$172.29K</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>28916.49</v>
+        <v>28891.49</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28950</v>
+        <v>28925</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -1552,12 +1692,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-$31.43K</t>
+          <t>-$13.10K</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>+$47.15K</t>
+          <t>+$55.01K</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1568,139 +1708,139 @@
       <c r="G8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>28918.46</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>705</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>-$62.25M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+$71.89M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A9" s="5" t="n">
+        <v>28906.49</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>28940</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>+$10.48K</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
+        <v>28916.49</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>28950</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-$31.43K</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>+$47.15K</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>28918.46</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>-$47.01M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$57.77M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
         <v>28936.49</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B12" s="5" t="n">
         <v>28970</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>+$10.48K</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>28941.49</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>28975</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$60.24K</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$65.48K</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>28966.49</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>29000</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>-$115.25K</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>+$162.40K</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>28991.49</v>
+        <v>28941.49</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>29025</v>
+        <v>28975</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1709,12 +1849,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-$40.74K</t>
+          <t>-$60.24K</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>+$46.57K</t>
+          <t>+$65.48K</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1725,87 +1865,87 @@
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>29016.49</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>29050</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>28966.49</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>-$20.37K</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+$90.22K</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-$115.25K</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$162.40K</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>29041.49</v>
+        <v>28991.49</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>29075</v>
+        <v>29025</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>+$2.91K</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-$40.74K</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>+$37.83K</t>
+          <t>+$46.57K</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>29041.66</v>
+        <v>29016.49</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>708</v>
+        <v>29050</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>-$9.22M</t>
+          <t>-$20.37K</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>+$12.58M</t>
+          <t>+$90.22K</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1816,116 +1956,120 @@
       <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>29066.49</v>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>29100</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="A17" s="5" t="n">
+        <v>29041.49</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>29075</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>-$96.04K</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>+$305.59K</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>+$2.91K</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>+$37.83K</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>29091.49</v>
+        <v>29041.66</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>29125</v>
+        <v>708</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>-$13.64M</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>+$25.78M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>29066.49</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>29100</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>-$69.85K</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$145.52K</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>29116.49</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>29150</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>-$14.55K</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>+$253.20K</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-$96.04K</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>+$305.59K</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>29123.8</v>
+        <v>29091.49</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>710</v>
+        <v>29125</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>-$11.42M</t>
+          <t>-$69.85K</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>+$31.70M</t>
+          <t>+$145.52K</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -1937,105 +2081,101 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>29136.49</v>
+        <v>29116.49</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>29170</v>
+        <v>29150</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>+$58.21K</t>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>-$14.55K</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>+$75.67K</t>
+          <t>+$253.20K</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>29141.49</v>
+        <v>29123.8</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>29175</v>
+        <v>710</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>-$5.15M</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>+$48.04M</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>29136.49</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>29170</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+$29.10K</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>+$157.16K</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>29166.49</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>29200</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>-$253.20K</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>+$323.05K</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>+$58.21K</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>+$75.67K</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>29186.49</v>
+        <v>29141.49</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29220</v>
+        <v>29175</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -2049,48 +2189,44 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>+$64.03K</t>
+          <t>+$157.16K</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>29191.49</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>29225</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="A25" s="2" t="n">
+        <v>29166.49</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>29200</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>-$23.28K</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>+$75.67K</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>-$253.20K</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>+$323.05K</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -2098,10 +2234,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>29206.49</v>
+        <v>29186.49</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>29240</v>
+        <v>29220</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -2110,12 +2246,12 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>+$49.48K</t>
+          <t>+$29.10K</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>+$72.76K</t>
+          <t>+$64.03K</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2130,33 +2266,33 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>29216.49</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>29250</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="A27" s="5" t="n">
+        <v>29191.49</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>29225</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>-$75.67K</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>+$215.37K</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>-$23.28K</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>+$75.67K</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -2164,10 +2300,10 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>29226.49</v>
+        <v>29206.49</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>29260</v>
+        <v>29240</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2176,12 +2312,12 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>+$40.74K</t>
+          <t>+$49.48K</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>+$46.57K</t>
+          <t>+$72.76K</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2196,123 +2332,230 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>29241.49</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>29275</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="A29" s="2" t="n">
+        <v>29216.49</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>29250</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>-$5.82K</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>+$46.57K</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>-$75.67K</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>+$215.37K</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>29329.13</v>
+        <v>29226.49</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>715</v>
+        <v>29260</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>+$685.61K</t>
+          <t>+$40.74K</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>+$32.26M</t>
+          <t>+$46.57K</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
+        <v>29241.49</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>29275</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>-$5.82K</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>+$46.57K</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>29329.13</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>+$24.11M</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>+$52.70M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
         <v>29452.33</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B33" s="5" t="n">
         <v>718</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>+$1.04M</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>+$23.44M</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>+$4.35M</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>+$25.11M</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="G33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29493.4</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>719</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>-$775.31K</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>+$9.48M</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
         <v>29534.46</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B35" s="2" t="n">
         <v>720</v>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>+$4.19M</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>+$21.18M</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>+$16.68M</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>+$26.64M</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2387,12 +2630,12 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>-$7.01M</t>
+          <t>-$7.00M</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>+$7.02M</t>
+          <t>+$7.01M</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -2416,12 +2659,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>-$29.24M</t>
+          <t>-$27.15M</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+$29.46M</t>
+          <t>+$27.48M</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2449,12 +2692,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>-$2.80M</t>
+          <t>-$3.13M</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>+$2.81M</t>
+          <t>+$3.21M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2482,12 +2725,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>-$54.73M</t>
+          <t>-$56.02M</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+$54.85M</t>
+          <t>+$56.55M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2515,12 +2758,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>-$7.44M</t>
+          <t>-$6.37M</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>+$7.65M</t>
+          <t>+$10.52M</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2535,130 +2778,134 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>2897.28</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>-$16.38M</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+$17.17M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-$26.06M</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+$37.97M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
+        <v>2907.34</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>-$4.90M</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>+$13.44M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>2917.4</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>-$69.29M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+$76.20M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>-$46.53M</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>+$85.89M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>2927.46</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>291</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>-$3.16M</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>+$16.75M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>+$34.81M</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>+$53.96M</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2937.52</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-$23.23M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$27.68M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
@@ -2674,14 +2921,14 @@
           <t>IWM</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$3.48M</t>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>+$8.84M</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>+$19.11M</t>
+          <t>+$31.10M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -2704,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2754,267 +3001,201 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>97.76000000000001</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>+$1.46M</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>+$1.68M</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>-$182.64K</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>+$2.82M</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>99.06</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>+$1.44M</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+$2.02M</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>98.41</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>+$180.63K</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>+$218.94K</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>-$886.65K</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>+$1.72M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>99.06</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>+$1.84M</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>+$1.85M</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>+$4.26M</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+$7.28M</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>99.39</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>+$85.51K</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>+$85.51K</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>+$412.09K</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>+$1.72M</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>101.02</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>104.28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>+$5.82M</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>+$6.03M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>+$8.89M</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+$9.02M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>102.65</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+$278.47K</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>+$280.58K</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>104.28</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>+$4.48M</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>+$4.53M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>114.05</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>175</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>+$946.35K</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>+$947.12K</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3435,7 +3616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3509,12 +3690,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>-$180.38M</t>
+          <t>-$155.05M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+$192.97M</t>
+          <t>+$248.56M</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -3535,10 +3716,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7654.54</v>
+        <v>7574.4</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -3547,12 +3728,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>-$81.90M</t>
+          <t>-$171.90M</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>+$127.25M</t>
+          <t>+$184.64M</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3573,10 +3754,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7574.4</v>
+        <v>7654.54</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -3585,12 +3766,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-$112.05M</t>
+          <t>-$42.09M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>+$119.12M</t>
+          <t>+$106.57M</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -3623,12 +3804,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>-$69.29M</t>
+          <t>-$46.53M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>+$76.20M</t>
+          <t>+$85.89M</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3643,42 +3824,38 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>28918.46</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>705</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-$62.25M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>+$71.89M</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>7604.45</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>758</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-$20.57M</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>+$67.82M</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3719,68 +3896,64 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>4308.17</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>393</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>-$58.55M</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>+$59.46M</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>7674.58</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>+$23.93M</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>+$62.50M</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2867.1</v>
+        <v>4308.17</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>285</v>
+        <v>393</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-$54.73M</t>
+          <t>-$58.55M</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>+$54.85M</t>
+          <t>+$59.46M</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -3795,64 +3968,68 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>7674.58</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>+$6.02M</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>+$49.95M</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>28918.46</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>-$47.01M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>+$57.77M</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7661.05</v>
+        <v>2867.1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7650</v>
+        <v>285</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>-$2.95M</t>
+          <t>-$56.02M</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>+$36.05M</t>
+          <t>+$56.55M</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3869,104 +4046,116 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2927.46</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>+$34.81M</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>+$53.96M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>29329.13</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>715</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>+$24.11M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>+$52.70M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>7604.45</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>758</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B14" s="2" t="n">
+        <v>7524.31</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-$20.95M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+$35.22M</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>7724.67</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>+$18.54M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+$34.95M</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7611.05</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>7600</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>-$2.36M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+$34.76M</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-$45.40M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+$49.32M</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -3975,24 +4164,24 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>29329.13</v>
+        <v>29123.8</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>+$685.61K</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>-$5.15M</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>+$32.26M</t>
+          <t>+$48.04M</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -4005,172 +4194,180 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>29123.8</v>
+        <v>7614.47</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>710</v>
+        <v>759</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>-$11.42M</t>
+          <t>-$5.22M</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>+$31.70M</t>
+          <t>+$47.45M</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>28713.13</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>700</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-$26.08M</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>+$30.56M</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>7644.52</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>762</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>+$16.37M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+$41.09M</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7661.05</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7650</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-$3.15M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>+$38.54M</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>7644.52</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>762</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>+$3.09M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>+$29.91M</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>7524.31</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>-$26.80M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>+$29.47M</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2897.28</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-$26.06M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+$37.97M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2816.8</v>
+        <v>28713.13</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>-$29.24M</t>
+          <t>-$30.25M</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>+$29.46M</t>
+          <t>+$37.03M</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -4187,28 +4384,28 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2937.52</v>
+        <v>7724.67</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>292</v>
+        <v>770</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>-$23.23M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>+$34.85M</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>+$27.68M</t>
+          <t>+$35.65M</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -4218,7 +4415,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4229,24 +4426,24 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7711.05</v>
+        <v>7611.05</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>+$4.78M</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>-$2.27M</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>+$25.15M</t>
+          <t>+$33.40M</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -4257,254 +4454,254 @@
       <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>7511.05</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>-$21.92M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>+$23.81M</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2967.7</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>+$8.84M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+$31.10M</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>7711.05</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>+$5.85M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>+$30.82M</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2816.8</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>-$27.15M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>+$27.48M</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B26" s="2" t="n">
+        <v>29534.46</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>+$16.68M</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>+$26.64M</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>29041.66</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>708</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>-$13.64M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+$25.78M</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>29452.33</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>718</v>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>+$1.04M</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>+$23.44M</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>+$4.35M</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>+$25.11M</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>29534.46</v>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>720</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>+$4.19M</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>+$21.18M</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>7641.05</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>7630</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="B29" s="2" t="n">
+        <v>7686.05</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>7675</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>+$5.36M</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>+$21.05M</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>7686.05</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>7675</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>+$12.19M</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>+$20.68M</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>+$14.22M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+$24.13M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>7561.05</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>7550</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>-$18.08M</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>+$20.03M</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>2967.7</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>295</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>-$3.48M</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>+$19.11M</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4513,10 +4710,10 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>7646.05</v>
+        <v>7641.05</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>7635</v>
+        <v>7630</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -4525,58 +4722,58 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>+$7.86M</t>
+          <t>+$5.45M</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>+$18.20M</t>
+          <t>+$21.41M</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>2897.28</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>288</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>-$16.38M</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>+$17.17M</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>7511.05</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>-$17.54M</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>+$19.05M</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4585,130 +4782,138 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>7601.05</v>
+        <v>7646.05</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>7590</v>
+        <v>7635</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>-$7.67M</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>+$8.12M</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>+$16.79M</t>
+          <t>+$18.82M</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>2927.46</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>291</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>-$3.16M</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>+$16.75M</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>7671.05</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>+$10.06M</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>+$17.94M</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>7671.05</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>7660</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="B34" s="2" t="n">
+        <v>7561.05</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>7550</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>+$9.23M</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>+$16.47M</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>-$15.75M</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>+$17.44M</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>29041.66</v>
+        <v>7601.05</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>708</v>
+        <v>7590</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>-$9.22M</t>
+          <t>-$7.19M</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>+$12.58M</t>
+          <t>+$15.72M</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -4719,38 +4924,38 @@
       <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>7581.05</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>7570</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="B36" s="5" t="n">
+        <v>7691.05</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>7680</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>-$10.77M</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>+$11.90M</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>+$4.11M</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>+$15.64M</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4763,24 +4968,24 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>7584.42</v>
+        <v>7696.05</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>756</v>
+        <v>7685</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>-$7.50M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>+$9.32M</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>+$11.20M</t>
+          <t>+$14.72M</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -4797,138 +5002,142 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>28507.8</v>
+        <v>7676.05</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>695</v>
+        <v>7665</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>-$10.32M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>+$5.17M</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>+$10.78M</t>
+          <t>+$13.87M</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>4298.4</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>-$9.44M</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>+$10.76M</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>7534.33</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>751</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>-$10.08M</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>+$13.56M</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>7501.05</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>7490</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>-$8.77M</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>+$8.85M</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>2907.34</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>-$4.90M</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>+$13.44M</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>4479.38</v>
+        <v>28507.8</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>99</v>
+        <v>695</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>+$3.96M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>-$12.81M</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>+$8.20M</t>
+          <t>+$13.32M</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -4941,142 +5150,146 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>28631</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>698</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>-$10.83M</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>+$11.52M</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>4298.4</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>-$9.44M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$10.76M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>7581.05</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>-$9.66M</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>+$10.68M</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B45" s="5" t="n">
         <v>2892.25</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C45" s="5" t="n">
         <v>287.5</v>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>-$7.44M</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>+$7.65M</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-$6.37M</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>+$10.52M</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>4406.83</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>402</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>-$6.60M</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$7.45M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>2766.5</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>-$7.01M</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>+$7.02M</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>4569.87</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>+$6.78M</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>+$6.93M</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5085,36 +5298,40 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>4439.71</v>
+        <v>29493.4</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>405</v>
+        <v>719</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>+$685.04K</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>-$775.31K</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>+$6.38M</t>
+          <t>+$9.48M</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -5123,10 +5340,10 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>101.02</v>
+        <v>104.28</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -5135,12 +5352,12 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>+$5.82M</t>
+          <t>+$8.89M</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>+$6.03M</t>
+          <t>+$9.02M</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5155,190 +5372,178 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>104.28</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>+$4.48M</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>+$4.53M</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>28302.46</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>690</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>-$8.23M</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>+$8.41M</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>7576.05</v>
+        <v>4479.38</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>7565</v>
+        <v>99</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-$2.92M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>+$3.96M</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>+$4.20M</t>
+          <t>+$8.20M</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>28754.2</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>701</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>-$4.61M</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>+$7.71M</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>4162.66</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>-$3.49M</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>+$3.69M</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>28795.26</v>
+        <v>4406.83</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>702</v>
+        <v>402</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>-$2.61M</t>
+          <t>-$6.60M</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>+$3.48M</t>
+          <t>+$7.45M</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>2836.92</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>-$2.80M</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$2.81M</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>+$4.26M</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$7.28M</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5347,28 +5552,28 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>4072.16</v>
+        <v>2766.5</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>90</v>
+        <v>275</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>-$2.53M</t>
+          <t>-$7.00M</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>+$2.66M</t>
+          <t>+$7.01M</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -5381,28 +5586,28 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>99.06</v>
+        <v>4569.87</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>+$1.84M</t>
+          <t>+$6.78M</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>+$1.85M</t>
+          <t>+$6.93M</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5417,292 +5622,284 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>7506.05</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>7495</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="B55" s="2" t="n">
+        <v>7501.05</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>7490</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-$1.67M</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>+$1.85M</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>-$6.74M</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>+$6.81M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>97.76000000000001</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>+$1.46M</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>+$1.68M</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>4439.71</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>+$685.04K</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>+$6.38M</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>7576.05</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>7565</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>-$2.61M</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>+$3.75M</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>4253.15</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="B58" s="2" t="n">
+        <v>4162.66</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-$842.97K</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>+$1.39M</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>7516.05</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>7505</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-$975.69K</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>+$1.19M</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>-$3.49M</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>+$3.69M</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>114.05</v>
+        <v>2836.92</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>+$946.35K</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>-$3.13M</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>+$947.12K</t>
+          <t>+$3.21M</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>97.76000000000001</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>-$182.64K</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>+$2.82M</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>4373.94</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>399</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>-$149.38K</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>+$660.68K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>29166.49</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>29200</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-$253.20K</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>+$323.05K</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="B61" s="5" t="n">
+        <v>4072.16</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-$2.53M</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>+$2.66M</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>29066.49</v>
+        <v>99.06</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>29100</v>
+        <v>152</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>-$96.04K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>+$1.44M</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>+$305.59K</t>
+          <t>+$2.02M</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -5712,7 +5909,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -5723,24 +5920,24 @@
         </is>
       </c>
       <c r="B63" s="5" t="n">
-        <v>102.65</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>+$278.47K</t>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>-$886.65K</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>+$280.58K</t>
+          <t>+$1.72M</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -5757,62 +5954,66 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B64" s="5" t="n">
-        <v>29116.49</v>
+        <v>101.67</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>29150</v>
+        <v>156</v>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>-$14.55K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>+$412.09K</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>+$253.20K</t>
+          <t>+$1.72M</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
-        <v>98.41</v>
+        <v>7506.05</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>151</v>
+        <v>7495</v>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>+$180.63K</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>-$1.31M</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>+$218.94K</t>
+          <t>+$1.45M</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -5822,191 +6023,199 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>4253.15</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-$842.97K</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>+$1.39M</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>7516.05</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>7505</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-$746.11K</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>+$907.97K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>4373.94</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>399</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>-$149.38K</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>+$660.68K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>29166.49</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>29200</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-$253.20K</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>+$323.05K</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>29216.49</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>29250</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="B70" s="2" t="n">
+        <v>29066.49</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>29100</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>-$75.67K</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>+$215.37K</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>-$96.04K</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>+$305.59K</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>28866.49</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>28900</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-$158.32K</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>+$172.29K</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>28966.49</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>29000</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>-$115.25K</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>+$162.40K</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>29141.49</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>29175</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>+$29.10K</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>+$157.16K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>29091.49</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>29125</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>-$69.85K</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>+$145.52K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -6015,10 +6224,10 @@
         </is>
       </c>
       <c r="B71" s="5" t="n">
-        <v>29016.49</v>
+        <v>29116.49</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>29050</v>
+        <v>29150</v>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
@@ -6027,12 +6236,12 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>-$20.37K</t>
+          <t>-$14.55K</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>+$90.22K</t>
+          <t>+$253.20K</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -6043,116 +6252,116 @@
       <c r="H71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>99.39</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>+$85.51K</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>+$85.51K</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>29216.49</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>29250</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>-$75.67K</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>+$215.37K</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n">
-        <v>29191.49</v>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>29225</v>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="B73" s="2" t="n">
+        <v>28866.49</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>28900</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>-$23.28K</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>+$75.67K</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>-$158.32K</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>+$172.29K</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n">
-        <v>29136.49</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>29170</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="B74" s="2" t="n">
+        <v>28966.49</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>+$58.21K</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>+$75.67K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>-$115.25K</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>+$162.40K</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -6163,10 +6372,10 @@
         </is>
       </c>
       <c r="B75" s="5" t="n">
-        <v>29206.49</v>
+        <v>29141.49</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>29240</v>
+        <v>29175</v>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
@@ -6175,24 +6384,20 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>+$49.48K</t>
+          <t>+$29.10K</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>+$72.76K</t>
+          <t>+$157.16K</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -6201,10 +6406,10 @@
         </is>
       </c>
       <c r="B76" s="5" t="n">
-        <v>28941.49</v>
+        <v>29091.49</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>28975</v>
+        <v>29125</v>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
@@ -6213,12 +6418,12 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>-$60.24K</t>
+          <t>-$69.85K</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>+$65.48K</t>
+          <t>+$145.52K</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -6235,36 +6440,32 @@
         </is>
       </c>
       <c r="B77" s="5" t="n">
-        <v>29186.49</v>
+        <v>29016.49</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>29220</v>
+        <v>29050</v>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>+$29.10K</t>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>-$20.37K</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>+$64.03K</t>
+          <t>+$90.22K</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -6273,10 +6474,10 @@
         </is>
       </c>
       <c r="B78" s="5" t="n">
-        <v>28891.49</v>
+        <v>29191.49</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>28925</v>
+        <v>29225</v>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
@@ -6285,20 +6486,24 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>-$13.10K</t>
+          <t>-$23.28K</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>+$55.01K</t>
+          <t>+$75.67K</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -6307,32 +6512,36 @@
         </is>
       </c>
       <c r="B79" s="5" t="n">
-        <v>28916.49</v>
+        <v>29136.49</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>28950</v>
+        <v>29170</v>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-$31.43K</t>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>+$58.21K</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>+$47.15K</t>
+          <t>+$75.67K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -6341,32 +6550,36 @@
         </is>
       </c>
       <c r="B80" s="5" t="n">
-        <v>29241.49</v>
+        <v>29206.49</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>29275</v>
+        <v>29240</v>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>-$5.82K</t>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>+$49.48K</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>+$46.57K</t>
+          <t>+$72.76K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -6375,10 +6588,10 @@
         </is>
       </c>
       <c r="B81" s="5" t="n">
-        <v>28991.49</v>
+        <v>28941.49</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>29025</v>
+        <v>28975</v>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
@@ -6387,12 +6600,12 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>-$40.74K</t>
+          <t>-$60.24K</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>+$46.57K</t>
+          <t>+$65.48K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -6409,10 +6622,10 @@
         </is>
       </c>
       <c r="B82" s="5" t="n">
-        <v>29226.49</v>
+        <v>29186.49</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>29260</v>
+        <v>29220</v>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
@@ -6421,12 +6634,12 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>+$40.74K</t>
+          <t>+$29.10K</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>+$46.57K</t>
+          <t>+$64.03K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -6447,36 +6660,32 @@
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>29041.49</v>
+        <v>28891.49</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>29075</v>
+        <v>28925</v>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>+$2.91K</t>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>-$13.10K</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>+$37.83K</t>
+          <t>+$55.01K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -6485,36 +6694,32 @@
         </is>
       </c>
       <c r="B84" s="5" t="n">
-        <v>28906.49</v>
+        <v>28916.49</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>28940</v>
+        <v>28950</v>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>$0</t>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>-$31.43K</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>+$10.48K</t>
+          <t>+$47.15K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -6523,39 +6728,221 @@
         </is>
       </c>
       <c r="B85" s="5" t="n">
+        <v>29241.49</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>29275</v>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>-$5.82K</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>+$46.57K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>28991.49</v>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>29025</v>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>-$40.74K</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>+$46.57K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>29226.49</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>29260</v>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>+$40.74K</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>+$46.57K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>29041.49</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>29075</v>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>+$2.91K</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>+$37.83K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>28906.49</v>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>28940</v>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>+$10.48K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
         <v>28936.49</v>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C90" s="5" t="n">
         <v>28970</v>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>+$10.48K</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H85"/>
+  <autoFilter ref="A1:H90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>